--- a/artfynd/A 59719-2024 artfynd.xlsx
+++ b/artfynd/A 59719-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>112550310</v>
       </c>
       <c r="B2" t="n">
-        <v>89661</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,37 +788,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112550313</v>
+        <v>112550312</v>
       </c>
       <c r="B3" t="n">
-        <v>89679</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -837,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>526326</v>
+        <v>526198</v>
       </c>
       <c r="R3" t="n">
-        <v>6984803</v>
+        <v>6984921</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -914,12 +904,7 @@
         <v>112550308</v>
       </c>
       <c r="B4" t="n">
-        <v>89625</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1032,12 +1017,7 @@
         <v>112550309</v>
       </c>
       <c r="B5" t="n">
-        <v>78809</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,37 +1127,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112550312</v>
+        <v>112550311</v>
       </c>
       <c r="B6" t="n">
-        <v>90343</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1191,10 +1166,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>526198</v>
+        <v>526186</v>
       </c>
       <c r="R6" t="n">
-        <v>6984921</v>
+        <v>6984926</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1258,124 +1233,6 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>112550311</v>
-      </c>
-      <c r="B7" t="n">
-        <v>56513</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Rundeln, Jmt</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>526186</v>
-      </c>
-      <c r="R7" t="n">
-        <v>6984926</v>
-      </c>
-      <c r="S7" t="n">
-        <v>10</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Bräcke</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Nyhem</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2023-09-06</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2023-09-06</t>
-        </is>
-      </c>
-      <c r="AD7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>1 substratenheter</t>
-        </is>
-      </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>Sebastian Acker</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>Sebastian Acker</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
         </is>

--- a/artfynd/A 59719-2024 artfynd.xlsx
+++ b/artfynd/A 59719-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -785,6 +790,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112550310</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -898,6 +908,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112550312</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1011,6 +1026,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112550308</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1124,6 +1144,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112550309</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1237,8 +1262,20 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112550311</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>